--- a/outputs/results/zones/mites.xlsx
+++ b/outputs/results/zones/mites.xlsx
@@ -7,13 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="test 2" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="alive 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="venom 2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="untreated" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="venom 1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="test 1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="dead 1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="dead" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="alive" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,10 +18,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -64,8 +67,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -153,7 +159,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6667500" cy="5715000"/>
+    <ext cx="6667500" cy="34290000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -161,6 +167,81 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>18</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3105150" cy="1066800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>18</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3086100" cy="1028700"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>18</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2952750" cy="1028700"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -183,7 +264,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6667500" cy="3810000"/>
+    <ext cx="6667500" cy="20955000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -201,26 +282,21 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6667500" cy="5715000"/>
+    <ext cx="3105150" cy="1028700"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -231,26 +307,21 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6667500" cy="9525000"/>
+    <ext cx="2914650" cy="1028700"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -261,86 +332,21 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>18</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6667500" cy="5715000"/>
+    <ext cx="2924175" cy="990600"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6667500" cy="3810000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6667500" cy="3810000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -643,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,6 +661,14 @@
       <c r="B1" t="n">
         <v>1</v>
       </c>
+      <c r="C1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>first recording detections</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -662,7 +676,12 @@
           <t>mite_0000</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>dead</t>
         </is>
@@ -674,7 +693,12 @@
           <t>mite_0001</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>dead</t>
         </is>
@@ -683,22 +707,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mite_0003</t>
+          <t>mite_0002</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mite_0012</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
+          <t>mite_0003</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>dead</t>
         </is>
@@ -707,10 +741,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mite_0016</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
+          <t>mite_0005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>dead</t>
         </is>
@@ -719,16 +758,517 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>mite_0006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mite_0007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mite_0010</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mite_0011</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mite_0012</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mite_0013</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mite_0015</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mite_0016</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mite_0017</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mite_0020</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mite_0024</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mite_0029</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mite_0030</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>mite_0031</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mite_0032</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mite_0033</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>mite_0036</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mite_0038</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>mite_0039</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>mite_0040</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mite_0041</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>mite_0042</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>mite_0046</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>mite_0047</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>mite_0048</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>mite_0049</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>mite_0053</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>mite_0055</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>mite_0056</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>mite_0058</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>dead</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="S1:U1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -740,7 +1280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,14 +1292,27 @@
       <c r="B1" t="n">
         <v>1</v>
       </c>
+      <c r="C1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>first recording detections</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mite_0002</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
+          <t>mite_0004</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>dead</t>
         </is>
@@ -768,10 +1321,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mite_0009</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
+          <t>mite_0008</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>dead</t>
         </is>
@@ -780,180 +1338,49 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mite_0019</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>mite ID</t>
-        </is>
-      </c>
-      <c r="B1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mite_0004</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mite_0013</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mite_0029</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
+          <t>mite_0009</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>alive</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>alive</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mite_0032</t>
+          <t>mite_0018</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mite_0036</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>mite ID</t>
-        </is>
-      </c>
-      <c r="B1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mite_0005</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mite_0008</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mite_0010</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>mite_0011</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>mite_0015</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
+          <t>mite_0019</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>dead</t>
         </is>
@@ -962,10 +1389,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mite_0027</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+          <t>mite_0021</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>alive</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>alive</t>
         </is>
@@ -974,22 +1406,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mite_0030</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
+          <t>mite_0022</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>alive</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>alive</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mite_0033</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
+          <t>mite_0023</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>dead</t>
         </is>
@@ -998,235 +1440,228 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>mite_0025</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mite_0026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mite_0027</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mite_0028</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>alive</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>alive</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mite_0034</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mite_0035</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>alive</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>alive</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>mite_0037</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mite_0043</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mite_0044</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mite_0045</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>mite_0050</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mite_0051</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mite_0052</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>dead</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>mite ID</t>
-        </is>
-      </c>
-      <c r="B1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mite_0006</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mite_0014</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mite_0018</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>mite_0020</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>mite_0035</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>mite ID</t>
-        </is>
-      </c>
-      <c r="B1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mite_0007</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mite_0017</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mite_0025</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>mite_0034</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>mite ID</t>
-        </is>
-      </c>
-      <c r="B1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mite_0021</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>mite_0022</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>mite_0024</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="S1:U1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/outputs/results/zones/mites.xlsx
+++ b/outputs/results/zones/mites.xlsx
@@ -659,9 +659,6 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" t="n">
         <v>2</v>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -681,11 +678,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -698,11 +690,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -715,11 +702,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -732,11 +714,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -749,11 +726,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -766,11 +738,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -783,11 +750,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -800,11 +762,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -817,11 +774,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -834,11 +786,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -851,11 +798,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -868,11 +810,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -885,11 +822,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -902,11 +834,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -919,11 +846,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -936,11 +858,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -953,11 +870,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -970,11 +882,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -987,11 +894,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1004,11 +906,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1021,11 +918,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1038,11 +930,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1055,11 +942,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1072,11 +954,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1089,11 +966,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1106,11 +978,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1123,11 +990,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1140,11 +1002,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1157,11 +1014,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1174,11 +1026,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1191,11 +1038,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1208,11 +1050,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1225,11 +1062,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1242,11 +1074,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1255,11 +1082,6 @@
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>dead</t>
         </is>
@@ -1290,9 +1112,6 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" t="n">
         <v>2</v>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -1312,11 +1131,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1329,11 +1143,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1346,11 +1155,6 @@
           <t>alive</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1363,11 +1167,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1380,11 +1179,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1397,11 +1191,6 @@
           <t>alive</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1414,11 +1203,6 @@
           <t>alive</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1431,11 +1215,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1448,11 +1227,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1465,11 +1239,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1482,11 +1251,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1499,11 +1263,6 @@
           <t>alive</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1516,11 +1275,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1533,11 +1287,6 @@
           <t>alive</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>alive</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1550,11 +1299,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1567,11 +1311,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1584,11 +1323,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1601,11 +1335,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1618,11 +1347,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1635,11 +1359,6 @@
           <t>dead</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1648,11 +1367,6 @@
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>dead</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>dead</t>
         </is>
